--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -7,7 +7,8 @@
     <sheet name="Properties" sheetId="2" r:id="rId2"/>
     <sheet name="Income" sheetId="3" r:id="rId3"/>
     <sheet name="Spending" sheetId="4" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" r:id="rId5"/>
+    <sheet name="Household" sheetId="5" r:id="rId5"/>
+    <sheet name="Assumptions" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -432,7 +433,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -441,6 +442,8 @@
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="33.83203125" customWidth="1"/>
     <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" customWidth="1"/>
+    <col min="9" max="9" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,22 +468,29 @@
       <c r="G1" t="str">
         <v>Net sale proceeds $</v>
       </c>
+      <c r="H1" t="str">
+        <v>Rent real growth %/yr</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Costs real growth %/yr</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -496,20 +506,26 @@
       <c r="D1" t="str">
         <v>To year</v>
       </c>
+      <c r="E1" t="str">
+        <v>Real growth %/yr</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:E1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="42.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="29.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,15 +535,75 @@
       <c r="B1" t="str">
         <v>$/mo (excl. property costs &amp; healthcare)</v>
       </c>
+      <c r="C1" t="str">
+        <v>From year (blank = from start)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>To year (blank = perpetual)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Real growth %/yr</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I1"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="29.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Role (spouse or dependent)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Current age</v>
+      </c>
+      <c r="D1" t="str">
+        <v>SS start age</v>
+      </c>
+      <c r="E1" t="str">
+        <v>SS $/mo (pre-haircut)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>SS haircut %</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Health pre-65 $/yr</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Health 65+ $/yr</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Employer coverage until age</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>

--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -554,17 +554,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="29.83203125" customWidth="1"/>
+    <col min="7" max="7" width="23.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" customWidth="1"/>
+    <col min="11" max="11" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,27 +580,33 @@
         <v>Current age</v>
       </c>
       <c r="D1" t="str">
+        <v>Lump-sum cost $</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Lump-sum year</v>
+      </c>
+      <c r="F1" t="str">
         <v>SS start age</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>SS $/mo (pre-haircut)</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>SS haircut %</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>Health pre-65 $/yr</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>Health 65+ $/yr</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>Employer coverage until age</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -554,19 +554,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="23.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="17.83203125" customWidth="1"/>
-    <col min="11" max="11" width="29.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" customWidth="1"/>
+    <col min="12" max="12" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -580,33 +581,36 @@
         <v>Current age</v>
       </c>
       <c r="D1" t="str">
-        <v>Lump-sum cost $</v>
+        <v>Support cost $/yr</v>
       </c>
       <c r="E1" t="str">
-        <v>Lump-sum year</v>
+        <v>From year</v>
       </c>
       <c r="F1" t="str">
+        <v>Through year</v>
+      </c>
+      <c r="G1" t="str">
         <v>SS start age</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>SS $/mo (pre-haircut)</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>SS haircut %</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Health pre-65 $/yr</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Health 65+ $/yr</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Employer coverage until age</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -402,31 +402,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:H1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="49.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="54.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" customWidth="1"/>
+    <col min="7" max="7" width="47.83203125" customWidth="1"/>
+    <col min="8" max="8" width="48.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Type (taxable, traditional_ira, 401k, roth_ira)</v>
+      </c>
+      <c r="C1" t="str">
         <v>Balance $</v>
       </c>
-      <c r="B1" t="str">
-        <v>Real return %/yr</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
+      <c r="D1" t="str">
+        <v>Cost basis $ (taxable only; blank = same as balance)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Your contribution $/yr</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Employer match $/yr</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Contribute until age (blank = work-until age)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Contribution increase %/yr (blank = inflation)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -442,8 +458,8 @@
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="33.83203125" customWidth="1"/>
     <col min="7" max="7" width="21.83203125" customWidth="1"/>
-    <col min="8" max="8" width="23.83203125" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" customWidth="1"/>
+    <col min="9" max="9" width="41.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,10 +485,10 @@
         <v>Net sale proceeds $</v>
       </c>
       <c r="H1" t="str">
-        <v>Rent real growth %/yr</v>
+        <v>Rent increase %/yr (blank = inflation)</v>
       </c>
       <c r="I1" t="str">
-        <v>Costs real growth %/yr</v>
+        <v>Costs increase %/yr (blank = inflation)</v>
       </c>
     </row>
   </sheetData>
@@ -490,7 +506,7 @@
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,7 +523,7 @@
         <v>To year</v>
       </c>
       <c r="E1" t="str">
-        <v>Real growth %/yr</v>
+        <v>Increase %/yr (blank = inflation)</v>
       </c>
     </row>
   </sheetData>
@@ -525,7 +541,7 @@
     <col min="2" max="2" width="42.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="29.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,7 +558,7 @@
         <v>To year (blank = perpetual)</v>
       </c>
       <c r="E1" t="str">
-        <v>Real growth %/yr</v>
+        <v>Increase %/yr (blank = inflation)</v>
       </c>
     </row>
   </sheetData>
@@ -617,7 +633,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C23"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -670,122 +686,210 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>social.startAge</v>
+        <v>economy.inflationPct</v>
       </c>
       <c r="B5">
-        <v>67</v>
+        <v>2.5</v>
       </c>
       <c r="C5" t="str">
-        <v>Social Security start age (years)</v>
+        <v>inflation %/yr (plain number, 2.5 = 2.5%)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>social.monthly</v>
+        <v>buckets.preservationReturnPct</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="C6" t="str">
-        <v>Social Security $/mo, today's dollars, pre-haircut</v>
+        <v>capital preservation return %/yr, before inflation</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>social.haircutPct</v>
+        <v>buckets.incomeReturnPct</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>5.5</v>
       </c>
       <c r="C7" t="str">
-        <v>% cut applied to Social Security (plain number, 25 = 25%)</v>
+        <v>high income return %/yr, before inflation</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>health.preMedicareAnnual</v>
+        <v>buckets.equitiesReturnPct</v>
       </c>
       <c r="B8">
-        <v>16000</v>
+        <v>9.5</v>
       </c>
       <c r="C8" t="str">
-        <v>healthcare $/yr before 65, after employer coverage ends</v>
+        <v>global equities return %/yr, before inflation</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>health.postMedicareAnnual</v>
+        <v>buckets.preservationYears</v>
       </c>
       <c r="B9">
-        <v>7500</v>
+        <v>8</v>
       </c>
       <c r="C9" t="str">
-        <v>healthcare $/yr from age 65</v>
+        <v>years of withdrawals held in capital preservation (years 1 to N)</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>health.employerCoverageUntilAge</v>
+        <v>buckets.incomeThroughYear</v>
       </c>
       <c r="B10">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C10" t="str">
-        <v>age employer health coverage ends</v>
+        <v>high income holds years N+1 through this year; equities hold the rest</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>endState.mode</v>
-      </c>
-      <c r="B11" t="str">
-        <v>zero</v>
+        <v>taxes.ordinaryIncomePct</v>
+      </c>
+      <c r="B11">
+        <v>22</v>
       </c>
       <c r="C11" t="str">
-        <v>one of: zero, bequest, floor</v>
+        <v>effective tax % on traditional IRA / 401(k) withdrawals (federal + state)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>endState.bequest</v>
+        <v>taxes.capitalGainsPct</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C12" t="str">
-        <v>$ to leave (used when mode is bequest)</v>
+        <v>effective tax % on gains when selling in a taxable account (federal + state)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>endState.floor</v>
+        <v>social.startAge</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C13" t="str">
-        <v>$ the balance never drops below (used when mode is floor)</v>
+        <v>Social Security start age (years)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>work.untilAge</v>
+        <v>social.monthly</v>
       </c>
       <c r="B14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C14" t="str">
-        <v>willing-to-work-until age (the solver's income window)</v>
+        <v>Social Security $/mo, today's dollars, pre-haircut</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v># Inflation is NOT an input; returns are real (after inflation and tax)</v>
+        <v>social.haircutPct</v>
+      </c>
+      <c r="B15">
+        <v>25</v>
+      </c>
+      <c r="C15" t="str">
+        <v>% cut applied to Social Security (plain number, 25 = 25%)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>health.preMedicareAnnual</v>
+      </c>
+      <c r="B16">
+        <v>16000</v>
+      </c>
+      <c r="C16" t="str">
+        <v>healthcare $/yr before 65, after employer coverage ends</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>health.postMedicareAnnual</v>
+      </c>
+      <c r="B17">
+        <v>7500</v>
+      </c>
+      <c r="C17" t="str">
+        <v>healthcare $/yr from age 65</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>health.employerCoverageUntilAge</v>
+      </c>
+      <c r="B18">
+        <v>40</v>
+      </c>
+      <c r="C18" t="str">
+        <v>age employer health coverage ends</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>endState.mode</v>
+      </c>
+      <c r="B19" t="str">
+        <v>zero</v>
+      </c>
+      <c r="C19" t="str">
+        <v>one of: zero, bequest, floor</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>endState.bequest</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20" t="str">
+        <v>$ to leave (used when mode is bequest)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>endState.floor</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21" t="str">
+        <v>$ the balance never drops below (used when mode is floor)</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>work.untilAge</v>
+      </c>
+      <c r="B22">
+        <v>50</v>
+      </c>
+      <c r="C22" t="str">
+        <v>willing-to-work-until age (the solver's income window)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v># Amounts are in today's dollars; rates are actual (before inflation)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="49.83203125" customWidth="1"/>
@@ -410,8 +410,10 @@
     <col min="4" max="4" width="54.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
     <col min="6" max="6" width="21.83203125" customWidth="1"/>
-    <col min="7" max="7" width="47.83203125" customWidth="1"/>
+    <col min="7" max="7" width="36.83203125" customWidth="1"/>
     <col min="8" max="8" width="48.83203125" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" customWidth="1"/>
+    <col min="10" max="10" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,15 +436,21 @@
         <v>Employer match $/yr</v>
       </c>
       <c r="G1" t="str">
-        <v>Contribute until age (blank = work-until age)</v>
+        <v>Contribute for how many more years</v>
       </c>
       <c r="H1" t="str">
         <v>Contribution increase %/yr (blank = inflation)</v>
       </c>
+      <c r="I1" t="str">
+        <v>Invested in (buckets or own)</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Own fund return %/yr (used when invested in own)</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -879,7 +887,7 @@
         <v>50</v>
       </c>
       <c r="C22" t="str">
-        <v>willing-to-work-until age (the solver's income window)</v>
+        <v>for the 'or earn $X/yr' answer: extra income is earned through this age</v>
       </c>
     </row>
     <row r="23">

--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -641,7 +641,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -881,23 +881,12 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>work.untilAge</v>
-      </c>
-      <c r="B22">
-        <v>50</v>
-      </c>
-      <c r="C22" t="str">
-        <v>for the 'or earn $X/yr' answer: extra income is earned through this age</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
         <v># Amounts are in today's dollars; rates are actual (before inflation)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -4,11 +4,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Accounts" sheetId="1" r:id="rId1"/>
-    <sheet name="Properties" sheetId="2" r:id="rId2"/>
-    <sheet name="Income" sheetId="3" r:id="rId3"/>
-    <sheet name="Spending" sheetId="4" r:id="rId4"/>
-    <sheet name="Household" sheetId="5" r:id="rId5"/>
-    <sheet name="Assumptions" sheetId="6" r:id="rId6"/>
+    <sheet name="Income" sheetId="2" r:id="rId2"/>
+    <sheet name="Spending" sheetId="3" r:id="rId3"/>
+    <sheet name="Household" sheetId="4" r:id="rId4"/>
+    <sheet name="Assumptions" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -402,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="49.83203125" customWidth="1"/>
@@ -414,6 +413,7 @@
     <col min="8" max="8" width="48.83203125" customWidth="1"/>
     <col min="9" max="9" width="30.83203125" customWidth="1"/>
     <col min="10" max="10" width="50.83203125" customWidth="1"/>
+    <col min="11" max="11" width="49.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,66 +447,18 @@
       <c r="J1" t="str">
         <v>Own fund return %/yr (used when invested in own)</v>
       </c>
+      <c r="K1" t="str">
+        <v>Own fund swing %/yr (used when invested in own)</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="19.83203125" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" customWidth="1"/>
-    <col min="6" max="6" width="33.83203125" customWidth="1"/>
-    <col min="7" max="7" width="21.83203125" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" customWidth="1"/>
-    <col min="9" max="9" width="41.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Rent $/mo</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Costs $/mo</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Mortgage P&amp;I $/mo</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Payoff year</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Sale year (leave empty to keep)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Net sale proceeds $</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Rent increase %/yr (blank = inflation)</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Costs increase %/yr (blank = inflation)</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E1"/>
   <cols>
@@ -541,12 +493,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="42.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="29.83203125" customWidth="1"/>
     <col min="5" max="5" width="35.83203125" customWidth="1"/>
@@ -557,7 +509,7 @@
         <v>Name</v>
       </c>
       <c r="B1" t="str">
-        <v>$/mo (excl. property costs &amp; healthcare)</v>
+        <v>$/mo (excl. healthcare)</v>
       </c>
       <c r="C1" t="str">
         <v>From year (blank = from start)</v>
@@ -576,7 +528,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L1"/>
   <cols>
@@ -639,9 +591,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C26"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -760,133 +712,177 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>taxes.ordinaryIncomePct</v>
+        <v>buckets.preservationVolPct</v>
       </c>
       <c r="B11">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C11" t="str">
-        <v>effective tax % on traditional IRA / 401(k) withdrawals (federal + state)</v>
+        <v>capital preservation's typical yearly swing %, for the simulation</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>taxes.capitalGainsPct</v>
+        <v>buckets.incomeVolPct</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C12" t="str">
-        <v>effective tax % on gains when selling in a taxable account (federal + state)</v>
+        <v>high income's typical yearly swing %</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>social.startAge</v>
+        <v>buckets.equitiesVolPct</v>
       </c>
       <c r="B13">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="C13" t="str">
-        <v>Social Security start age (years)</v>
+        <v>global equities' typical yearly swing %</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>social.monthly</v>
+        <v>simulation.targetSuccessPct</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C14" t="str">
-        <v>Social Security $/mo, today's dollars, pre-haircut</v>
+        <v>the plan should work in this % of simulated futures (the gap aims for it)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>social.haircutPct</v>
+        <v>taxes.ordinaryIncomePct</v>
       </c>
       <c r="B15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C15" t="str">
-        <v>% cut applied to Social Security (plain number, 25 = 25%)</v>
+        <v>effective tax % on traditional IRA / 401(k) withdrawals (federal + state)</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>health.preMedicareAnnual</v>
+        <v>taxes.capitalGainsPct</v>
       </c>
       <c r="B16">
-        <v>16000</v>
+        <v>15</v>
       </c>
       <c r="C16" t="str">
-        <v>healthcare $/yr before 65, after employer coverage ends</v>
+        <v>effective tax % on gains when selling in a taxable account (federal + state)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>health.postMedicareAnnual</v>
+        <v>social.startAge</v>
       </c>
       <c r="B17">
-        <v>7500</v>
+        <v>67</v>
       </c>
       <c r="C17" t="str">
-        <v>healthcare $/yr from age 65</v>
+        <v>Social Security start age (years)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>health.employerCoverageUntilAge</v>
+        <v>social.monthly</v>
       </c>
       <c r="B18">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C18" t="str">
-        <v>age employer health coverage ends</v>
+        <v>Social Security $/mo, today's dollars, pre-haircut</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>endState.mode</v>
-      </c>
-      <c r="B19" t="str">
-        <v>zero</v>
+        <v>social.haircutPct</v>
+      </c>
+      <c r="B19">
+        <v>25</v>
       </c>
       <c r="C19" t="str">
-        <v>one of: zero, bequest, floor</v>
+        <v>% cut applied to Social Security (plain number, 25 = 25%)</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>endState.bequest</v>
+        <v>health.preMedicareAnnual</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="C20" t="str">
-        <v>$ to leave (used when mode is bequest)</v>
+        <v>healthcare $/yr before 65, after employer coverage ends</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>endState.floor</v>
+        <v>health.postMedicareAnnual</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="C21" t="str">
-        <v>$ the balance never drops below (used when mode is floor)</v>
+        <v>healthcare $/yr from age 65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
+        <v>health.employerCoverageUntilAge</v>
+      </c>
+      <c r="B22">
+        <v>40</v>
+      </c>
+      <c r="C22" t="str">
+        <v>age employer health coverage ends</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>endState.mode</v>
+      </c>
+      <c r="B23" t="str">
+        <v>zero</v>
+      </c>
+      <c r="C23" t="str">
+        <v>one of: zero, bequest, floor</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>endState.bequest</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24" t="str">
+        <v>$ to leave (used when mode is bequest)</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>endState.floor</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25" t="str">
+        <v>$ the balance never drops below (used when mode is floor)</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
         <v># Amounts are in today's dollars; rates are actual (before inflation)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C26"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -495,13 +495,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="29.83203125" customWidth="1"/>
     <col min="5" max="5" width="35.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,10 +521,13 @@
       <c r="E1" t="str">
         <v>Increase %/yr (blank = inflation)</v>
       </c>
+      <c r="F1" t="str">
+        <v>Variable (yes/no)</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -593,7 +597,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -660,7 +664,7 @@
         <v>buckets.preservationReturnPct</v>
       </c>
       <c r="B6">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="str">
         <v>capital preservation return %/yr, before inflation</v>
@@ -671,7 +675,7 @@
         <v>buckets.incomeReturnPct</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="str">
         <v>high income return %/yr, before inflation</v>
@@ -682,7 +686,7 @@
         <v>buckets.equitiesReturnPct</v>
       </c>
       <c r="B8">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="C8" t="str">
         <v>global equities return %/yr, before inflation</v>
@@ -756,133 +760,144 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>taxes.ordinaryIncomePct</v>
+        <v>simulation.spendMorePct</v>
       </c>
       <c r="B15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" t="str">
-        <v>effective tax % on traditional IRA / 401(k) withdrawals (federal + state)</v>
+        <v>spend more scenario: % increase on variable spending lines</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>taxes.capitalGainsPct</v>
+        <v>taxes.ordinaryIncomePct</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C16" t="str">
-        <v>effective tax % on gains when selling in a taxable account (federal + state)</v>
+        <v>effective tax % on traditional IRA / 401(k) withdrawals (federal + state)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>social.startAge</v>
+        <v>taxes.capitalGainsPct</v>
       </c>
       <c r="B17">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="C17" t="str">
-        <v>Social Security start age (years)</v>
+        <v>effective tax % on gains when selling in a taxable account (federal + state)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>social.monthly</v>
+        <v>social.startAge</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C18" t="str">
-        <v>Social Security $/mo, today's dollars, pre-haircut</v>
+        <v>Social Security start age (years)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>social.haircutPct</v>
+        <v>social.monthly</v>
       </c>
       <c r="B19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C19" t="str">
-        <v>% cut applied to Social Security (plain number, 25 = 25%)</v>
+        <v>Social Security $/mo, today's dollars, pre-haircut</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>health.preMedicareAnnual</v>
+        <v>social.haircutPct</v>
       </c>
       <c r="B20">
-        <v>16000</v>
+        <v>25</v>
       </c>
       <c r="C20" t="str">
-        <v>healthcare $/yr before 65, after employer coverage ends</v>
+        <v>% cut applied to Social Security (plain number, 25 = 25%)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>health.postMedicareAnnual</v>
+        <v>health.preMedicareAnnual</v>
       </c>
       <c r="B21">
-        <v>7500</v>
+        <v>16000</v>
       </c>
       <c r="C21" t="str">
-        <v>healthcare $/yr from age 65</v>
+        <v>healthcare $/yr before 65, after employer coverage ends</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>health.employerCoverageUntilAge</v>
+        <v>health.postMedicareAnnual</v>
       </c>
       <c r="B22">
-        <v>40</v>
+        <v>7500</v>
       </c>
       <c r="C22" t="str">
-        <v>age employer health coverage ends</v>
+        <v>healthcare $/yr from age 65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>endState.mode</v>
-      </c>
-      <c r="B23" t="str">
-        <v>zero</v>
+        <v>health.employerCoverageUntilAge</v>
+      </c>
+      <c r="B23">
+        <v>40</v>
       </c>
       <c r="C23" t="str">
-        <v>one of: zero, bequest, floor</v>
+        <v>age employer health coverage ends</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>endState.bequest</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
+        <v>endState.mode</v>
+      </c>
+      <c r="B24" t="str">
+        <v>zero</v>
       </c>
       <c r="C24" t="str">
-        <v>$ to leave (used when mode is bequest)</v>
+        <v>one of: zero, bequest, floor</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>endState.floor</v>
+        <v>endState.bequest</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25" t="str">
-        <v>$ the balance never drops below (used when mode is floor)</v>
+        <v>$ to leave (used when mode is bequest)</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
+        <v>endState.floor</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26" t="str">
+        <v>$ the balance never drops below (used when mode is floor)</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
         <v># Amounts are in today's dollars; rates are actual (before inflation)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C27"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="49.83203125" customWidth="1"/>
@@ -414,6 +414,7 @@
     <col min="9" max="9" width="30.83203125" customWidth="1"/>
     <col min="10" max="10" width="50.83203125" customWidth="1"/>
     <col min="11" max="11" width="49.83203125" customWidth="1"/>
+    <col min="12" max="12" width="34.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,10 +451,13 @@
       <c r="K1" t="str">
         <v>Own fund swing %/yr (used when invested in own)</v>
       </c>
+      <c r="L1" t="str">
+        <v>Owner (self or spouse; for RMDs)</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:J1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="49.83203125" customWidth="1"/>
@@ -411,10 +411,8 @@
     <col min="6" max="6" width="21.83203125" customWidth="1"/>
     <col min="7" max="7" width="36.83203125" customWidth="1"/>
     <col min="8" max="8" width="48.83203125" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" customWidth="1"/>
-    <col min="10" max="10" width="50.83203125" customWidth="1"/>
-    <col min="11" max="11" width="49.83203125" customWidth="1"/>
-    <col min="12" max="12" width="34.83203125" customWidth="1"/>
+    <col min="9" max="9" width="58.83203125" customWidth="1"/>
+    <col min="10" max="10" width="34.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -443,21 +441,15 @@
         <v>Contribution increase %/yr (blank = inflation)</v>
       </c>
       <c r="I1" t="str">
-        <v>Invested in (buckets or own)</v>
+        <v>Invested in (buckets, preservation, income, or equities)</v>
       </c>
       <c r="J1" t="str">
-        <v>Own fund return %/yr (used when invested in own)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Own fund swing %/yr (used when invested in own)</v>
-      </c>
-      <c r="L1" t="str">
         <v>Owner (self or spouse; for RMDs)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -412,7 +412,7 @@
     <col min="7" max="7" width="36.83203125" customWidth="1"/>
     <col min="8" max="8" width="48.83203125" customWidth="1"/>
     <col min="9" max="9" width="58.83203125" customWidth="1"/>
-    <col min="10" max="10" width="34.83203125" customWidth="1"/>
+    <col min="10" max="10" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
         <v>Invested in (buckets, preservation, income, or equities)</v>
       </c>
       <c r="J1" t="str">
-        <v>Owner (self or spouse; for RMDs)</v>
+        <v>Owner (self or spouse; for RMDs and 59½)</v>
       </c>
     </row>
   </sheetData>

--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -593,7 +593,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C29"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -701,199 +701,221 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>buckets.incomeThroughYear</v>
+        <v>buckets.cashYears</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>high income holds years N+1 through this year; equities hold the rest</v>
+        <v>within capital preservation: years 1 to C as cash (shown in the results only)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>buckets.preservationVolPct</v>
+        <v>buckets.shortBondYears</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="str">
-        <v>capital preservation's typical yearly swing %, for the simulation</v>
+        <v>within capital preservation: years C+1 to S in short-term bonds; the rest medium-term (shown in the results only)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>buckets.incomeVolPct</v>
+        <v>buckets.incomeThroughYear</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C12" t="str">
-        <v>high income's typical yearly swing %</v>
+        <v>high income holds years N+1 through this year; equities hold the rest</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>buckets.equitiesVolPct</v>
+        <v>buckets.preservationVolPct</v>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C13" t="str">
-        <v>global equities' typical yearly swing %</v>
+        <v>capital preservation's typical yearly swing %, for the simulation</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>simulation.targetSuccessPct</v>
+        <v>buckets.incomeVolPct</v>
       </c>
       <c r="B14">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="C14" t="str">
-        <v>the plan should work in this % of simulated futures (the gap aims for it)</v>
+        <v>high income's typical yearly swing %</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>simulation.spendMorePct</v>
+        <v>buckets.equitiesVolPct</v>
       </c>
       <c r="B15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C15" t="str">
-        <v>spend more scenario: % increase on variable spending lines</v>
+        <v>global equities' typical yearly swing %</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>taxes.ordinaryIncomePct</v>
+        <v>simulation.targetSuccessPct</v>
       </c>
       <c r="B16">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="C16" t="str">
-        <v>effective tax % on traditional IRA / 401(k) withdrawals (federal + state)</v>
+        <v>the plan should work in this % of simulated futures (the gap aims for it)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>taxes.capitalGainsPct</v>
+        <v>simulation.spendMorePct</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C17" t="str">
-        <v>effective tax % on gains when selling in a taxable account (federal + state)</v>
+        <v>spend more scenario: % increase on variable spending lines</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>social.startAge</v>
+        <v>taxes.ordinaryIncomePct</v>
       </c>
       <c r="B18">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="C18" t="str">
-        <v>Social Security start age (years)</v>
+        <v>effective tax % on traditional IRA / 401(k) withdrawals (federal + state)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>social.monthly</v>
+        <v>taxes.capitalGainsPct</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C19" t="str">
-        <v>Social Security $/mo, today's dollars, pre-haircut</v>
+        <v>effective tax % on gains when selling in a taxable account (federal + state)</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>social.haircutPct</v>
+        <v>social.startAge</v>
       </c>
       <c r="B20">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="C20" t="str">
-        <v>% cut applied to Social Security (plain number, 25 = 25%)</v>
+        <v>Social Security start age (years)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>health.preMedicareAnnual</v>
+        <v>social.monthly</v>
       </c>
       <c r="B21">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="C21" t="str">
-        <v>healthcare $/yr before 65, after employer coverage ends</v>
+        <v>Social Security $/mo, today's dollars, pre-haircut</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>health.postMedicareAnnual</v>
+        <v>social.haircutPct</v>
       </c>
       <c r="B22">
-        <v>7500</v>
+        <v>25</v>
       </c>
       <c r="C22" t="str">
-        <v>healthcare $/yr from age 65</v>
+        <v>% cut applied to Social Security (plain number, 25 = 25%)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>health.employerCoverageUntilAge</v>
+        <v>health.preMedicareAnnual</v>
       </c>
       <c r="B23">
-        <v>40</v>
+        <v>16000</v>
       </c>
       <c r="C23" t="str">
-        <v>age employer health coverage ends</v>
+        <v>healthcare $/yr before 65, after employer coverage ends</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>endState.mode</v>
-      </c>
-      <c r="B24" t="str">
-        <v>zero</v>
+        <v>health.postMedicareAnnual</v>
+      </c>
+      <c r="B24">
+        <v>7500</v>
       </c>
       <c r="C24" t="str">
-        <v>one of: zero, bequest, floor</v>
+        <v>healthcare $/yr from age 65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>endState.bequest</v>
+        <v>health.employerCoverageUntilAge</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C25" t="str">
-        <v>$ to leave (used when mode is bequest)</v>
+        <v>age employer health coverage ends</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>endState.floor</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
+        <v>endState.mode</v>
+      </c>
+      <c r="B26" t="str">
+        <v>zero</v>
       </c>
       <c r="C26" t="str">
-        <v>$ the balance never drops below (used when mode is floor)</v>
+        <v>one of: zero, bequest, floor</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
+        <v>endState.bequest</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27" t="str">
+        <v>$ to leave (used when mode is bequest)</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>endState.floor</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28" t="str">
+        <v>$ the balance never drops below (used when mode is floor)</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
         <v># Amounts are in today's dollars; rates are actual (before inflation)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/template/runway-template.xlsx
+++ b/template/runway-template.xlsx
@@ -593,7 +593,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -712,210 +712,221 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>buckets.shortBondYears</v>
+        <v>buckets.liquidYears</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C11" t="str">
-        <v>within capital preservation: years C+1 to S in short-term bonds; the rest medium-term (shown in the results only)</v>
+        <v>while under 59½, the next N years of withdrawals must be covered by taxable accounts</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>buckets.incomeThroughYear</v>
+        <v>buckets.shortBondYears</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C12" t="str">
-        <v>high income holds years N+1 through this year; equities hold the rest</v>
+        <v>within capital preservation: years C+1 to S in short-term bonds; the rest medium-term (shown in the results only)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>buckets.preservationVolPct</v>
+        <v>buckets.incomeThroughYear</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C13" t="str">
-        <v>capital preservation's typical yearly swing %, for the simulation</v>
+        <v>high income holds years N+1 through this year; equities hold the rest</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>buckets.incomeVolPct</v>
+        <v>buckets.preservationVolPct</v>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>high income's typical yearly swing %</v>
+        <v>capital preservation's typical yearly swing %, for the simulation</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>buckets.equitiesVolPct</v>
+        <v>buckets.incomeVolPct</v>
       </c>
       <c r="B15">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C15" t="str">
-        <v>global equities' typical yearly swing %</v>
+        <v>high income's typical yearly swing %</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>simulation.targetSuccessPct</v>
+        <v>buckets.equitiesVolPct</v>
       </c>
       <c r="B16">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="C16" t="str">
-        <v>the plan should work in this % of simulated futures (the gap aims for it)</v>
+        <v>global equities' typical yearly swing %</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>simulation.spendMorePct</v>
+        <v>simulation.targetSuccessPct</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="C17" t="str">
-        <v>spend more scenario: % increase on variable spending lines</v>
+        <v>the plan should work in this % of simulated futures (the gap aims for it)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>taxes.ordinaryIncomePct</v>
+        <v>simulation.spendMorePct</v>
       </c>
       <c r="B18">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C18" t="str">
-        <v>effective tax % on traditional IRA / 401(k) withdrawals (federal + state)</v>
+        <v>spend more scenario: % increase on variable spending lines</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>taxes.capitalGainsPct</v>
+        <v>taxes.ordinaryIncomePct</v>
       </c>
       <c r="B19">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C19" t="str">
-        <v>effective tax % on gains when selling in a taxable account (federal + state)</v>
+        <v>effective tax % on traditional IRA / 401(k) withdrawals (federal + state)</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>social.startAge</v>
+        <v>taxes.capitalGainsPct</v>
       </c>
       <c r="B20">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="C20" t="str">
-        <v>Social Security start age (years)</v>
+        <v>effective tax % on gains when selling in a taxable account (federal + state)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>social.monthly</v>
+        <v>social.startAge</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C21" t="str">
-        <v>Social Security $/mo, today's dollars, pre-haircut</v>
+        <v>Social Security start age (years)</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>social.haircutPct</v>
+        <v>social.monthly</v>
       </c>
       <c r="B22">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C22" t="str">
-        <v>% cut applied to Social Security (plain number, 25 = 25%)</v>
+        <v>Social Security $/mo, today's dollars, pre-haircut</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>health.preMedicareAnnual</v>
+        <v>social.haircutPct</v>
       </c>
       <c r="B23">
-        <v>16000</v>
+        <v>25</v>
       </c>
       <c r="C23" t="str">
-        <v>healthcare $/yr before 65, after employer coverage ends</v>
+        <v>% cut applied to Social Security (plain number, 25 = 25%)</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>health.postMedicareAnnual</v>
+        <v>health.preMedicareAnnual</v>
       </c>
       <c r="B24">
-        <v>7500</v>
+        <v>16000</v>
       </c>
       <c r="C24" t="str">
-        <v>healthcare $/yr from age 65</v>
+        <v>healthcare $/yr before 65, after employer coverage ends</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>health.employerCoverageUntilAge</v>
+        <v>health.postMedicareAnnual</v>
       </c>
       <c r="B25">
-        <v>40</v>
+        <v>7500</v>
       </c>
       <c r="C25" t="str">
-        <v>age employer health coverage ends</v>
+        <v>healthcare $/yr from age 65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>endState.mode</v>
-      </c>
-      <c r="B26" t="str">
-        <v>zero</v>
+        <v>health.employerCoverageUntilAge</v>
+      </c>
+      <c r="B26">
+        <v>40</v>
       </c>
       <c r="C26" t="str">
-        <v>one of: zero, bequest, floor</v>
+        <v>age employer health coverage ends</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>endState.bequest</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
+        <v>endState.mode</v>
+      </c>
+      <c r="B27" t="str">
+        <v>zero</v>
       </c>
       <c r="C27" t="str">
-        <v>$ to leave (used when mode is bequest)</v>
+        <v>one of: zero, bequest, floor</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>endState.floor</v>
+        <v>endState.bequest</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28" t="str">
-        <v>$ the balance never drops below (used when mode is floor)</v>
+        <v>$ to leave (used when mode is bequest)</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
+        <v>endState.floor</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29" t="str">
+        <v>$ the balance never drops below (used when mode is floor)</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
         <v># Amounts are in today's dollars; rates are actual (before inflation)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C30"/>
   </ignoredErrors>
 </worksheet>
 </file>